--- a/output/xlsx/AdministradorAdicionaOperadorDeTerminal--GT-.xlsx
+++ b/output/xlsx/AdministradorAdicionaOperadorDeTerminal--GT-.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuario Administrador logado no sistema; Existe pelo menos um Terminal registrado.</t>
+    <t>Usuario Administrador deve ter feito login e obtido autorizacao do sistema.</t>
   </si>
   <si>
     <t>#</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">Postcondition: </t>
   </si>
   <si>
-    <t>Operador de Terminal salvo no sistema</t>
+    <t>Operador salvo no sistema</t>
   </si>
   <si>
     <t>TC2</t>
@@ -146,10 +146,10 @@
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Volta para listagem de Terminal</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Voltar'</t>
+    <t>Alternative Flow 3: Navega na lista de Terminais</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao de paginacao</t>
   </si>
   <si>
     <t>TC5</t>
